--- a/Hand_edited_log/1/student/anlpvhe187047/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/anlpvhe187047/TC4/GradeDetail.xlsx
@@ -1058,10 +1058,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1114,10 +1114,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1170,10 +1170,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1226,10 +1226,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1282,10 +1282,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1338,10 +1338,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>46</x:v>
@@ -1394,10 +1394,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
         <x:v>46</x:v>
@@ -1450,10 +1450,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>61</x:v>
@@ -1506,10 +1506,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>61</x:v>
@@ -1562,10 +1562,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>61</x:v>
@@ -1618,10 +1618,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4001</x:v>
+        <x:v>4002</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>55770</x:v>
+        <x:v>51734</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>61</x:v>
